--- a/docs/Milestone/CST-452_Test_Cases_SecureLink.xlsx
+++ b/docs/Milestone/CST-452_Test_Cases_SecureLink.xlsx
@@ -875,7 +875,7 @@
       <c r="B4" s="51" t="n"/>
       <c r="C4" s="42" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-27; TC-AUTH-07–10 on 2026-10-11</t>
         </is>
       </c>
       <c r="D4" s="53" t="n"/>
@@ -1321,60 +1321,244 @@
       </c>
       <c r="L13" s="69" t="n"/>
     </row>
-    <row r="14" s="39">
-      <c r="A14" s="69" t="n"/>
-      <c r="B14" s="69" t="n"/>
-      <c r="C14" s="69" t="n"/>
-      <c r="D14" s="69" t="n"/>
-      <c r="E14" s="69" t="n"/>
-      <c r="F14" s="69" t="n"/>
-      <c r="G14" s="69" t="n"/>
-      <c r="H14" s="69" t="n"/>
-      <c r="I14" s="69" t="n"/>
-      <c r="J14" s="69" t="n"/>
-      <c r="K14" s="69" t="n"/>
+    <row r="14" ht="95.25" customHeight="1" s="39">
+      <c r="A14" s="63" t="inlineStr">
+        <is>
+          <t>TC-AUTH-07</t>
+        </is>
+      </c>
+      <c r="B14" s="64" t="inlineStr">
+        <is>
+          <t>Sign-in token saved in Windows Credential Manager</t>
+        </is>
+      </c>
+      <c r="C14" s="64" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D14" s="64" t="inlineStr">
+        <is>
+          <t>TokenStore.Save(); ApiClient.AcceptToken()</t>
+        </is>
+      </c>
+      <c r="E14" s="64" t="inlineStr">
+        <is>
+          <t>Verify the sign-in token is kept in the Windows credential vault, not only in memory (US-24).</t>
+        </is>
+      </c>
+      <c r="F14" s="64" t="inlineStr">
+        <is>
+          <t>1. Sign in.
+2. Run `cmdkey /list`.
+3. Compare the stored token and expiry with the ones in use.</t>
+        </is>
+      </c>
+      <c r="G14" s="64" t="inlineStr">
+        <is>
+          <t>Test account</t>
+        </is>
+      </c>
+      <c r="H14" s="64" t="inlineStr">
+        <is>
+          <t>A generic credential named "SecureLink:AuthToken" exists; it holds the current token and its expiry time. The token is not written to any file.</t>
+        </is>
+      </c>
+      <c r="I14" s="64" t="inlineStr">
+        <is>
+          <t>after sign-in the token is in Windows Credential Manager: entry "SecureLink:AuthToken:test" listed by `cmdkey /list`=True; stored token equals the one in use=True; stored expiry is 60 minutes ahead</t>
+        </is>
+      </c>
+      <c r="J14" s="92" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="K14" s="64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Executed 2026-10-11 as Administrator by an automated harness that drives the client's own classes against the production backend and relays. The harness used a separate vault entry ("SecureLink:AuthToken:test") so the tester's own saved sign-in was not touched. </t>
+        </is>
+      </c>
       <c r="L14" s="69" t="n"/>
     </row>
-    <row r="15" s="39">
-      <c r="A15" s="69" t="n"/>
-      <c r="B15" s="69" t="n"/>
-      <c r="C15" s="69" t="n"/>
-      <c r="D15" s="69" t="n"/>
-      <c r="E15" s="69" t="n"/>
-      <c r="F15" s="69" t="n"/>
-      <c r="G15" s="69" t="n"/>
-      <c r="H15" s="69" t="n"/>
-      <c r="I15" s="69" t="n"/>
-      <c r="J15" s="69" t="n"/>
-      <c r="K15" s="69" t="n"/>
+    <row r="15" ht="108" customHeight="1" s="39">
+      <c r="A15" s="63" t="inlineStr">
+        <is>
+          <t>TC-AUTH-08</t>
+        </is>
+      </c>
+      <c r="B15" s="64" t="inlineStr">
+        <is>
+          <t>Saved sign-in restored on next launch</t>
+        </is>
+      </c>
+      <c r="C15" s="64" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D15" s="64" t="inlineStr">
+        <is>
+          <t>ApiClient.TryRestoreSessionAsync(); LoginWindow.TryResumeSessionAsync()</t>
+        </is>
+      </c>
+      <c r="E15" s="64" t="inlineStr">
+        <is>
+          <t>Verify the app signs in from the saved token on the next launch, without the password (US-24).</t>
+        </is>
+      </c>
+      <c r="F15" s="64" t="inlineStr">
+        <is>
+          <t>1. Sign in, then close the app.
+2. Start it again (nothing in memory, no password entered).
+3. Make an authenticated call.</t>
+        </is>
+      </c>
+      <c r="G15" s="64" t="inlineStr">
+        <is>
+          <t>Token saved by TC-AUTH-07</t>
+        </is>
+      </c>
+      <c r="H15" s="64" t="inlineStr">
+        <is>
+          <t>The saved sign-in is accepted and refreshed; authenticated calls succeed; the sign-in form is skipped and the main window opens.</t>
+        </is>
+      </c>
+      <c r="I15" s="64" t="inlineStr">
+        <is>
+          <t>a fresh ApiClient with no password restored the saved sign-in=True; authenticated call accepted (204); token was refreshed on restore (new token, expiry moved 2.1s later)=True</t>
+        </is>
+      </c>
+      <c r="J15" s="92" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="K15" s="64" t="inlineStr">
+        <is>
+          <t>Executed 2026-10-11 as Administrator by an automated harness that drives the client's own classes against the production backend and relays. The harness used a separate vault entry ("SecureLink:AuthToken:test") so the tester's own saved sign-in was not touched. The matching GUI behaviour is shown in the Milestone 6 screencast.</t>
+        </is>
+      </c>
       <c r="L15" s="69" t="n"/>
     </row>
-    <row r="16" s="39">
-      <c r="A16" s="69" t="n"/>
-      <c r="B16" s="69" t="n"/>
-      <c r="C16" s="69" t="n"/>
-      <c r="D16" s="69" t="n"/>
-      <c r="E16" s="69" t="n"/>
-      <c r="F16" s="69" t="n"/>
-      <c r="G16" s="69" t="n"/>
-      <c r="H16" s="69" t="n"/>
-      <c r="I16" s="69" t="n"/>
-      <c r="J16" s="69" t="n"/>
-      <c r="K16" s="69" t="n"/>
+    <row r="16" ht="108" customHeight="1" s="39">
+      <c r="A16" s="63" t="inlineStr">
+        <is>
+          <t>TC-AUTH-09</t>
+        </is>
+      </c>
+      <c r="B16" s="64" t="inlineStr">
+        <is>
+          <t>Saved sign-in rejected, expired, or signed out</t>
+        </is>
+      </c>
+      <c r="C16" s="64" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D16" s="64" t="inlineStr">
+        <is>
+          <t>ApiClient.TryRestoreSessionAsync(); ApiClient.SignOut(); MainWindow Sign out button</t>
+        </is>
+      </c>
+      <c r="E16" s="64" t="inlineStr">
+        <is>
+          <t>Verify a bad or unwanted saved sign-in is removed and the user is asked to sign in again (error conditions).</t>
+        </is>
+      </c>
+      <c r="F16" s="64" t="inlineStr">
+        <is>
+          <t>1. Alter the saved token, then launch.
+2. Save a token whose expiry has passed, then launch.
+3. Sign in, click Sign out, then launch.</t>
+        </is>
+      </c>
+      <c r="G16" s="64" t="inlineStr">
+        <is>
+          <t>Tampered token; expired token; valid token</t>
+        </is>
+      </c>
+      <c r="H16" s="64" t="inlineStr">
+        <is>
+          <t>In all three cases the sign-in is not restored, the vault entry is removed, and the sign-in form is shown.</t>
+        </is>
+      </c>
+      <c r="I16" s="64" t="inlineStr">
+        <is>
+          <t>tampered saved token: restore=False, entry removed=True. Expired saved token: restore=False, entry removed=True. Sign out: entry present before=True, removed from Credential Manager after=True, next launch restores=False</t>
+        </is>
+      </c>
+      <c r="J16" s="92" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="K16" s="64" t="inlineStr">
+        <is>
+          <t>Executed 2026-10-11 as Administrator by an automated harness that drives the client's own classes against the production backend and relays. The harness used a separate vault entry ("SecureLink:AuthToken:test") so the tester's own saved sign-in was not touched. The matching GUI behaviour is shown in the Milestone 6 screencast.</t>
+        </is>
+      </c>
       <c r="L16" s="69" t="n"/>
     </row>
-    <row r="17" s="39">
-      <c r="A17" s="69" t="n"/>
-      <c r="B17" s="69" t="n"/>
-      <c r="C17" s="69" t="n"/>
-      <c r="D17" s="69" t="n"/>
-      <c r="E17" s="69" t="n"/>
-      <c r="F17" s="69" t="n"/>
-      <c r="G17" s="69" t="n"/>
-      <c r="H17" s="69" t="n"/>
-      <c r="I17" s="69" t="n"/>
-      <c r="J17" s="69" t="n"/>
-      <c r="K17" s="69" t="n"/>
+    <row r="17" ht="69.75" customHeight="1" s="39">
+      <c r="A17" s="63" t="inlineStr">
+        <is>
+          <t>TC-AUTH-10</t>
+        </is>
+      </c>
+      <c r="B17" s="64" t="inlineStr">
+        <is>
+          <t>Token refresh endpoint</t>
+        </is>
+      </c>
+      <c r="C17" s="64" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D17" s="64" t="inlineStr">
+        <is>
+          <t>AuthController.Refresh()</t>
+        </is>
+      </c>
+      <c r="E17" s="64" t="inlineStr">
+        <is>
+          <t>Verify a still-valid token can be exchanged for a fresh one, and an invalid one cannot.</t>
+        </is>
+      </c>
+      <c r="F17" s="64" t="inlineStr">
+        <is>
+          <t>1. POST /api/auth/refresh with a valid token.
+2. Repeat with no token.
+3. Repeat with a token whose signature was altered.</t>
+        </is>
+      </c>
+      <c r="G17" s="64" t="inlineStr">
+        <is>
+          <t>Valid JWT; no JWT; tampered JWT</t>
+        </is>
+      </c>
+      <c r="H17" s="64" t="inlineStr">
+        <is>
+          <t>Step 1: 200 OK with a new token for the same user and a later expiry. Steps 2–3: 401 Unauthorized.</t>
+        </is>
+      </c>
+      <c r="I17" s="64" t="inlineStr">
+        <is>
+          <t>Valid token → 200 OK in 0.7 s; new token issued for the same user (same sub claim) with a later expiry; the new token was accepted by a protected endpoint (204). No token → 401. Tampered token → 401. GET instead of POST → 405.</t>
+        </is>
+      </c>
+      <c r="J17" s="92" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="K17" s="64" t="inlineStr">
+        <is>
+          <t>Executed 2026-10-11 against the production backend (https://165.227.213.133) after deploying the updated API.</t>
+        </is>
+      </c>
       <c r="L17" s="69" t="n"/>
     </row>
     <row r="18" s="39">
@@ -11339,7 +11523,7 @@
       <c r="B4" s="51" t="n"/>
       <c r="C4" s="42" t="inlineStr">
         <is>
-          <t>2026-09-27 (automated client harness)</t>
+          <t>2026-09-27 (automated client harness); TC-WG-07–08 on 2026-10-11</t>
         </is>
       </c>
       <c r="D4" s="53" t="n"/>
@@ -11783,32 +11967,125 @@
       </c>
       <c r="L13" s="63" t="n"/>
     </row>
-    <row r="14" s="39">
-      <c r="A14" s="63" t="n"/>
-      <c r="B14" s="63" t="n"/>
-      <c r="C14" s="63" t="n"/>
-      <c r="D14" s="63" t="n"/>
-      <c r="E14" s="63" t="n"/>
-      <c r="F14" s="63" t="n"/>
-      <c r="G14" s="63" t="n"/>
-      <c r="H14" s="63" t="n"/>
-      <c r="I14" s="63" t="n"/>
-      <c r="J14" s="63" t="n"/>
-      <c r="K14" s="63" t="n"/>
+    <row r="14" ht="69.75" customHeight="1" s="39">
+      <c r="A14" s="63" t="inlineStr">
+        <is>
+          <t>TC-WG-07</t>
+        </is>
+      </c>
+      <c r="B14" s="64" t="inlineStr">
+        <is>
+          <t>Tunnel health – healthy while connected</t>
+        </is>
+      </c>
+      <c r="C14" s="64" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D14" s="64" t="inlineStr">
+        <is>
+          <t>WireGuardInterop.GetLatestHandshakeUtc(); TunnelHealth.Evaluate()</t>
+        </is>
+      </c>
+      <c r="E14" s="64" t="inlineStr">
+        <is>
+          <t>Verify the app reads WireGuard's last-handshake time and reports a live tunnel as healthy (US-25).</t>
+        </is>
+      </c>
+      <c r="F14" s="64" t="inlineStr">
+        <is>
+          <t>1. Connect.
+2. Read the last handshake time.
+3. Evaluate tunnel health.</t>
+        </is>
+      </c>
+      <c r="G14" s="64" t="inlineStr">
+        <is>
+          <t>region=newyork</t>
+        </is>
+      </c>
+      <c r="H14" s="64" t="inlineStr">
+        <is>
+          <t>State is Establishing until the first handshake, then Healthy; the handshake time matches `wg show securelink latest-handshakes`.</t>
+        </is>
+      </c>
+      <c r="I14" s="64" t="inlineStr">
+        <is>
+          <t>right after connect the state was Establishing; ~5 s later: last handshake 6 s ago (wg reports unix time 1791702895), TunnelHealth = Healthy, IsHandshakeActive() = True; internet through tunnel → 200</t>
+        </is>
+      </c>
+      <c r="J14" s="92" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="K14" s="64" t="inlineStr">
+        <is>
+          <t>Executed 2026-10-11 as Administrator by an automated harness that drives the client's own classes against the production backend and relays. The matching GUI behaviour is shown in the Milestone 6 screencast.</t>
+        </is>
+      </c>
       <c r="L14" s="63" t="n"/>
     </row>
-    <row r="15" s="39">
-      <c r="A15" s="63" t="n"/>
-      <c r="B15" s="63" t="n"/>
-      <c r="C15" s="63" t="n"/>
-      <c r="D15" s="63" t="n"/>
-      <c r="E15" s="63" t="n"/>
-      <c r="F15" s="63" t="n"/>
-      <c r="G15" s="63" t="n"/>
-      <c r="H15" s="63" t="n"/>
-      <c r="I15" s="63" t="n"/>
-      <c r="J15" s="63" t="n"/>
-      <c r="K15" s="63" t="n"/>
+    <row r="15" ht="159" customHeight="1" s="39">
+      <c r="A15" s="63" t="inlineStr">
+        <is>
+          <t>TC-WG-08</t>
+        </is>
+      </c>
+      <c r="B15" s="64" t="inlineStr">
+        <is>
+          <t>Tunnel health – lost relay detected, then recovery</t>
+        </is>
+      </c>
+      <c r="C15" s="64" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D15" s="64" t="inlineStr">
+        <is>
+          <t>TunnelHealth.Evaluate(); MainWindow.CheckTunnelHealth()</t>
+        </is>
+      </c>
+      <c r="E15" s="64" t="inlineStr">
+        <is>
+          <t>Verify the app notices when the relay stops answering, instead of showing "Connected" indefinitely, and notices when it returns (US-25).</t>
+        </is>
+      </c>
+      <c r="F15" s="64" t="inlineStr">
+        <is>
+          <t>1. Connect.
+2. Remove this client's peer on the relay.
+3. Evaluate health every 5 seconds.
+4. Restore the peer on the relay.</t>
+        </is>
+      </c>
+      <c r="G15" s="64" t="inlineStr">
+        <is>
+          <t>region=newyork; peer removed with `wg set wg0 peer &lt;key&gt; remove`</t>
+        </is>
+      </c>
+      <c r="H15" s="64" t="inlineStr">
+        <is>
+          <t>Within about 180 seconds the state changes to Lost (the app shows "Connection lost") even though the tunnel service is still running. After the relay answers again the state returns to Healthy ("Connection restored").</t>
+        </is>
+      </c>
+      <c r="I15" s="64" t="inlineStr">
+        <is>
+          <t>healthy at start (Healthy). After the relay stopped answering, TunnelHealth became Lost in 171 s (last handshake then 182 s old; threshold 180 s) and IsHandshakeActive() = False, while the tunnel service was still RUNNING=True — the reason the app could not tell before. After the relay answered again, state returned to Healthy in 5 s. Run with a split tunnel (only the relay's tunnel address routed, no kill switch) so the PC's own internet stayed up throughout (200).</t>
+        </is>
+      </c>
+      <c r="J15" s="92" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="K15" s="64" t="inlineStr">
+        <is>
+          <t>Executed 2026-10-11 as Administrator by an automated harness that drives the client's own classes against the production backend and relays. A first attempt using the normal full tunnel was stopped by the tester: with the relay gone, the kill switch blocked all internet access during the 3-minute wait, exactly as designed. The test was re-run with a split tunnel so the wait would not interrupt the PC. The matching GUI behaviour is shown in the Milestone 6 screencast.</t>
+        </is>
+      </c>
       <c r="L15" s="63" t="n"/>
     </row>
     <row r="16" s="39">
